--- a/architectures and decision enablers/cloud-readiness-assessment-enabler/CRA_Calculator.xlsx
+++ b/architectures and decision enablers/cloud-readiness-assessment-enabler/CRA_Calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\cloud-readiness-assessment-enabler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7D6C90-A2C3-4FFC-9A18-C3E7DADF9662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C83D744-6EBB-4747-855F-63AAE5297DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EA83798-0DD6-40E8-BDD9-53B4FEBFB21D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6EA83798-0DD6-40E8-BDD9-53B4FEBFB21D}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs" sheetId="1" r:id="rId1"/>
@@ -1851,7 +1851,15 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>Cloud Adoption Framework (CAF) Maturity Profile</a:t>
+              <a:t>Cloud Readiness Assessment</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> </a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t> (CRA) Maturity Profile</a:t>
             </a:r>
           </a:p>
         </c:rich>
